--- a/Intersecciones/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
+++ b/Intersecciones/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-222439</t>
+          <t>I-513952</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,17 +508,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-9.9342378</t>
+          <t>-9.9292689</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-76.2435712</t>
+          <t>-76.2428934</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jr. 2 de Mayo / Jr. Mayro</t>
+          <t>Jirón Huallayco / Jirón Huánuco</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-222509</t>
+          <t>I-465027</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100101</t>
+          <t>100102</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -555,27 +555,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>AMARILIS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-9.9344671</t>
+          <t>-9.9262476</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-76.2432554</t>
+          <t>-76.1690544</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Jr. Mayro</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-222530</t>
+          <t>I-222400</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,22 +612,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-9.9317567</t>
+          <t>-9.9246359</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-76.2432038</t>
+          <t>-76.235783</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Jr. Abtao / Jr. Aguilar</t>
+          <t>Avenida Alameda de la República / Jirón 28 de Julio</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-326982</t>
+          <t>I-222442</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,22 +664,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-9.9389336</t>
+          <t>-9.9314103</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-76.2550199</t>
+          <t>-76.2416767</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Calle Visagaga</t>
+          <t>Jirón 2 de Mayo / Jirón Ayacucho</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-513952</t>
+          <t>I-222508</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -716,25 +716,493 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-9.9292689</t>
+          <t>-9.9317558</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-76.2428934</t>
+          <t>-76.2470128</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Jr. Huallayco / Jr. Huánuco</t>
+          <t>Jirón Leoncio Prado / Jirón Mayro</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>I-222568</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-9.9363079</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-76.2525909</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Jirón Provincias / Jirón Tarma / Pasaje Santa Isabel</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>I-555252</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-9.9234066</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-76.2376408</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Avenida Alameda de la República / Jirón Abtao</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>I-222509</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-9.9344671</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-76.2432554</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Jirón Mayro / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-326982</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-9.9389336</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-76.2550199</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Calle Visagaga / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I-465049</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>100102</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AMARILIS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-9.9259695</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-76.1675195</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>I-465041</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>100102</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AMARILIS</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-9.9252049</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-76.1728586</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>I-465040</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>100102</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AMARILIS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-9.9249279</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-76.1742184</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>I-465036</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100102</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AMARILIS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-9.9264972</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-76.1635928</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>I-465050</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>100102</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AMARILIS</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-9.9275478</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-76.1668087</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>100101</t>
         </is>

--- a/Intersecciones/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
+++ b/Intersecciones/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1208,6 +1208,162 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>I-465035</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>100102</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AMARILIS</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-9.923925</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-76.1752556</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>I-465486</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>100102</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AMARILIS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-9.9279489</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-76.1856381</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I-465051</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>100102</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AMARILIS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-9.9310603</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-76.1646692</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
+++ b/Intersecciones/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-513952</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>100101</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-9.9292689</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>100101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-465027</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>100102</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>AMARILIS</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-9.9262476</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>100101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-222400</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>100101</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-9.9246359</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>100101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-222442</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>100101</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-9.9314103</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>100101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-222508</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>100101</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-9.9317558</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>100101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-222568</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>100101</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-9.9363079</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>100101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-555252</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>100101</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-9.9234066</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>100101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-222509</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>100101</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-9.9344671</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>100101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-326982</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>100101</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-9.9389336</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>100101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-465049</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>100102</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AMARILIS</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-9.9259695</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>100101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-465041</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>100102</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AMARILIS</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-9.9252049</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>100101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-465040</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>100102</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AMARILIS</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-9.9249279</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>100101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-465036</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100102</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AMARILIS</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-9.9264972</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>100101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-465050</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>100102</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AMARILIS</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-9.9275478</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>100101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-465035</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>100102</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AMARILIS</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-9.923925</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>100101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-465486</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>100102</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AMARILIS</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-9.9279489</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>100101</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-465051</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>100102</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AMARILIS</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-9.9310603</t>
@@ -1356,11 +1271,6 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>100101</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
+++ b/Intersecciones/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
+++ b/Intersecciones/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
+++ b/Intersecciones/excels/HUANUCO-HUANUCO-HUANUCO.xlsx
@@ -486,27 +486,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-513952</t>
+          <t>I-555252</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-9.9292689</t>
+          <t>-9.9234066</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-76.2428934</t>
+          <t>-76.2376408</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jirón Huallayco / Jirón Huánuco</t>
+          <t>Avenida Alameda de la República / Jirón Abtao</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -533,27 +533,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-465027</t>
+          <t>I-513952</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-9.9262476</t>
+          <t>-9.9292689</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-76.1690544</t>
+          <t>-76.2428934</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jirón Huallayco / Jirón Huánuco</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -580,22 +580,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-222400</t>
+          <t>I-465486</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-9.9246359</t>
+          <t>-9.9279489</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-76.235783</t>
+          <t>-76.1856381</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Alameda de la República / Jirón 28 de Julio</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-222442</t>
+          <t>I-465051</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-9.9314103</t>
+          <t>-9.9310603</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-76.2416767</t>
+          <t>-76.1646692</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Jirón 2 de Mayo / Jirón Ayacucho</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-222508</t>
+          <t>I-465050</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-9.9317558</t>
+          <t>-9.9275478</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-76.2470128</t>
+          <t>-76.1668087</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Jirón Leoncio Prado / Jirón Mayro</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-222568</t>
+          <t>I-465049</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-9.9363079</t>
+          <t>-9.9259695</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-76.2525909</t>
+          <t>-76.1675195</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Jirón Provincias / Jirón Tarma / Pasaje Santa Isabel</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-555252</t>
+          <t>I-465041</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-9.9234066</t>
+          <t>-9.9252049</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-76.2376408</t>
+          <t>-76.1728586</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida Alameda de la República / Jirón Abtao</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -815,27 +815,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-222509</t>
+          <t>I-465040</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-9.9344671</t>
+          <t>-9.9249279</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-76.2432554</t>
+          <t>-76.1742184</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Jirón Mayro / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -862,27 +862,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-326982</t>
+          <t>I-465036</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-9.9389336</t>
+          <t>-9.9264972</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-76.2550199</t>
+          <t>-76.1635928</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Calle Visagaga / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -909,17 +909,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-465049</t>
+          <t>I-465035</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-9.9259695</t>
+          <t>-9.923925</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-76.1675195</t>
+          <t>-76.1752556</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-465041</t>
+          <t>I-465027</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-9.9252049</t>
+          <t>-9.9262476</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-76.1728586</t>
+          <t>-76.1690544</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1003,27 +1003,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-465040</t>
+          <t>I-326982</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-9.9249279</t>
+          <t>-9.9389336</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-76.1742184</t>
+          <t>-76.2550199</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle Visagaga / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1050,22 +1050,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-465036</t>
+          <t>I-222568</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-9.9264972</t>
+          <t>-9.9363079</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-76.1635928</t>
+          <t>-76.2525909</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jirón Provincias / Jirón Tarma / Pasaje Santa Isabel</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1097,27 +1097,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-465050</t>
+          <t>I-222509</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-9.9275478</t>
+          <t>-9.9344671</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-76.1668087</t>
+          <t>-76.2432554</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jirón Mayro / Calle s / n</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1144,22 +1144,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-465035</t>
+          <t>I-222508</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-9.923925</t>
+          <t>-9.9317558</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-76.1752556</t>
+          <t>-76.2470128</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jirón Leoncio Prado / Jirón Mayro</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1191,22 +1191,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-465486</t>
+          <t>I-222442</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-9.9279489</t>
+          <t>-9.9314103</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-76.1856381</t>
+          <t>-76.2416767</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jirón 2 de Mayo / Jirón Ayacucho</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1238,22 +1238,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-465051</t>
+          <t>I-222400</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-9.9310603</t>
+          <t>-9.9246359</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-76.1646692</t>
+          <t>-76.235783</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Alameda de la República / Jirón 28 de Julio</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
